--- a/backend/model/dataset_full.csv.xlsx
+++ b/backend/model/dataset_full.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Final year project\Final-Year-Project\backend\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0A3142-B897-47D3-B0C0-562396D730C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898DCA65-EEE9-4449-AB97-1AF3B9923BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E49CAF8F-777A-44D3-B548-E5417C8594C4}"/>
   </bookViews>

--- a/backend/model/dataset_full.csv.xlsx
+++ b/backend/model/dataset_full.csv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Final year project\Final-Year-Project\backend\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898DCA65-EEE9-4449-AB97-1AF3B9923BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61C1D18-8A24-4C70-A19D-5B5062BE8C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E49CAF8F-777A-44D3-B548-E5417C8594C4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E49CAF8F-777A-44D3-B548-E5417C8594C4}"/>
   </bookViews>
   <sheets>
     <sheet name="dataset_generated" sheetId="1" r:id="rId1"/>
